--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/INDIANA_2015.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/INDIANA_2015.xlsx
@@ -2652,7 +2652,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C128">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C305">
@@ -6439,7 +6439,7 @@
         <v>160</v>
       </c>
       <c r="D338">
-        <v>0.009100733746658325</v>
+        <v>0.009100733746658323</v>
       </c>
     </row>
     <row r="339">
@@ -14856,7 +14856,7 @@
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C806">
@@ -14874,7 +14874,7 @@
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C807">
@@ -15558,7 +15558,7 @@
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C845">
